--- a/processed_ruby_restored_xlsx/sc231_凛３：酔っ払ってＨ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc231_凛３：酔っ払ってＨ.ss.xlsx
@@ -545,8 +545,8 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>When it was time for dinner, Rin-chan showed up before
-being called.</t>
+          <t>When it was time for dinner, Rin-chan showed up
+before being called.</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -561,8 +561,8 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Maybe she was bored being alone without Miru-chan, who
-was usually with her.</t>
+          <t>Maybe she was bored being alone without Miru-chan,
+who was usually with her.</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -592,8 +592,8 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>「Alright, alright. Like I said earlier, I tried making
-an American Hamburg steak—how's that？」</t>
+          <t>「Alright, alright. Like I said earlier, I tried
+making an American Hamburg steak—how's that？」</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -716,7 +716,8 @@
       <c r="B17" s="1" t="inlineStr">
         <is>
           <t>「Yeah... I looked it up, and it says a hamburger made
-with ground beef is called an American hamburg steak.」</t>
+with ground beef is called an American hamburg
+steak.」</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -776,8 +777,8 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>「I make it with mixed ground meat like usual. It turns
-out more tender that way, you know.」</t>
+          <t>「I make it with mixed ground meat like usual. It
+turns out more tender that way, you know.」</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1338,8 +1339,8 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>If she's still about Rin-chan's age, after all, softer
-is better...</t>
+          <t>If she's still about Rin-chan's age, after all,
+softer is better...</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1551,7 +1552,8 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>Damn... did I mix up what Rin-chan and Miru-chan said?</t>
+          <t>Damn... did I mix up what Rin-chan and Miru-chan
+said?</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1869,8 +1871,8 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>...I'd rather avoid it if possible, but if that'll put
-Rin-chan in a good mood, it's a bargain, right？</t>
+          <t>...I'd rather avoid it if possible, but if that'll
+put Rin-chan in a good mood, it's a bargain, right？</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2084,8 +2086,8 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>She couldn't wait to eat her favorite treat she hadn't
-had in a long time.</t>
+          <t>She couldn't wait to eat her favorite treat she
+hadn't had in a long time.</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2510,8 +2512,8 @@
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan snatches three whiskey bonbons, rips open the
-wrapper, and stuffs them into her mouth.</t>
+          <t>Rin-chan snatches three whiskey bonbons, rips open
+the wrapper, and stuffs them into her mouth.</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -3062,7 +3064,8 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>「Nhi, nhihihihi... Jeez, just take it off already~~~！」</t>
+          <t>「Nhi, nhihihihi... Jeez, just take it off
+already~~~！」</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3644,8 +3647,8 @@
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>When I involuntarily caught my breath, Rin-chan rushed
-at me and I stumbled back on instinct.</t>
+          <t>When I involuntarily caught my breath, Rin-chan
+rushed at me and I stumbled back on instinct.</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -4042,8 +4045,8 @@
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t>…Well, it's no wonder I'd be upset being compared to a
-ridiculously impressive penis from manga.</t>
+          <t>…Well, it's no wonder I'd be upset being compared to
+a ridiculously impressive penis from manga.</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4059,8 +4062,8 @@
       <c r="B236" s="1" t="inlineStr">
         <is>
           <t>Besides, I've only seen a single stylized panel, so
-when I actually try to take it in it doesn't work like
-in the comic, and I look totally flustered.</t>
+when I actually try to take it in it doesn't work
+like in the comic, and I look totally flustered.</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4532,8 +4535,8 @@
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t>「Yeah, give it a kiss... um, like it says at the start
-of that page...」</t>
+          <t>「Yeah, give it a kiss... um, like it says at the
+start of that page...」</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4764,9 +4767,9 @@
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>In the manga, the guy's reactions to getting kissed on
-my penis are shown in speech bubbles, so I figured my
-reaction would be pretty much the same as in the
+          <t>In the manga, the guy's reactions to getting kissed
+on my penis are shown in speech bubbles, so I figured
+my reaction would be pretty much the same as in the
 comic.</t>
         </is>
       </c>
@@ -4873,8 +4876,8 @@
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan starts moving her head from side to side just
-like I said.</t>
+          <t>Rin-chan starts moving her head from side to side
+just like I said.</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -5289,8 +5292,8 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t>「It’s so melty... so tasty, mmm... smooch, nngh—smack！
-slurp, sluuuurp…」</t>
+          <t>「It’s so melty... so tasty, mmm... smooch,
+nngh—smack！ slurp, sluuuurp…」</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -5427,7 +5430,8 @@
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t>「Haa, phew... Maybe it's a little early for Rin-chan.」</t>
+          <t>「Haa, phew... Maybe it's a little early for
+Rin-chan.」</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -5504,8 +5508,8 @@
       <c r="B330" s="1" t="inlineStr">
         <is>
           <t>Rin-chan stirred the juice she’d been holding back
-inside her mouth, mixing it with a wet, guchu sound as
-if savoring it.</t>
+inside her mouth, mixing it with a wet, guchu sound
+as if savoring it.</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5672,8 +5676,8 @@
       </c>
       <c r="B341" s="1" t="inlineStr">
         <is>
-          <t>That's a sexy gesture too, but her expression suddenly
-clouds.</t>
+          <t>That's a sexy gesture too, but her expression
+suddenly clouds.</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -6211,8 +6215,8 @@
       </c>
       <c r="B376" s="1" t="inlineStr">
         <is>
-          <t>Her saliva mixed in, and it really felt like her mouth
-had become a pussy.</t>
+          <t>Her saliva mixed in, and it really felt like her
+mouth had become a pussy.</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -6409,7 +6413,8 @@
       </c>
       <c r="B389" s="1" t="inlineStr">
         <is>
-          <t>She's drunk, so does she not realize she'll bite down？</t>
+          <t>She's drunk, so does she not realize she'll bite
+down？</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -6516,7 +6521,8 @@
       <c r="B396" s="1" t="inlineStr">
         <is>
           <t>Rin-chan tucked her lips inward, using them to soften
-her teeth, and then she took it into her mouth again…！</t>
+her teeth, and then she took it into her mouth
+again…！</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -6640,7 +6646,8 @@
       </c>
       <c r="B404" s="1" t="inlineStr">
         <is>
-          <t>That made me involuntarily let out a moan of pleasure.</t>
+          <t>That made me involuntarily let out a moan of
+pleasure.</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -6715,8 +6722,8 @@
       </c>
       <c r="B409" s="1" t="inlineStr">
         <is>
-          <t>Sensing my weakness, Rin-chan gets indignant and moves
-her face even more vigorously back and forth.</t>
+          <t>Sensing my weakness, Rin-chan gets indignant and
+moves her face even more vigorously back and forth.</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -6793,8 +6800,8 @@
       </c>
       <c r="B414" s="1" t="inlineStr">
         <is>
-          <t>Right on the brink of orgasm, and when the pleasure is
-pushed even higher I can't stand it！</t>
+          <t>Right on the brink of orgasm, and when the pleasure
+is pushed even higher I can't stand it！</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -6871,8 +6878,8 @@
       </c>
       <c r="B419" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan watches me as my voice trembles with pleasure
-and smiles, clearly enjoying it.</t>
+          <t>Rin-chan watches me as my voice trembles with
+pleasure and smiles, clearly enjoying it.</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -6887,8 +6894,8 @@
       </c>
       <c r="B420" s="1" t="inlineStr">
         <is>
-          <t>At that moment, the saliva that had pooled in my mouth
-overflowed and clung to the penis.</t>
+          <t>At that moment, the saliva that had pooled in my
+mouth overflowed and clung to the penis.</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -6904,8 +6911,8 @@
       <c r="B421" s="1" t="inlineStr">
         <is>
           <t>An indescribable warmth flushed my body, and I fell
-into the illusion that each nerve was being singed one
-by one.</t>
+into the illusion that each nerve was being singed
+one by one.</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -6935,8 +6942,8 @@
       </c>
       <c r="B423" s="1" t="inlineStr">
         <is>
-          <t>「Fuu, nmm-chup！ Rin... ah！ Okuhii... it feels so good,
-hngh...！」</t>
+          <t>「Fuu, nmm-chup！ Rin... ah！ Okuhii... it feels so
+good, hngh...！」</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -7059,8 +7066,8 @@
       </c>
       <c r="B431" s="1" t="inlineStr">
         <is>
-          <t>When I looked down thinking that, Rin-chan's cheek was
-puffed out just where the penis was.</t>
+          <t>When I looked down thinking that, Rin-chan's cheek
+was puffed out just where the penis was.</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -7557,8 +7564,8 @@
       </c>
       <c r="B463" s="1" t="inlineStr">
         <is>
-          <t>「Yaaaah！ Chuchubbu！ Give me more... don’t stop, leeeet
-me have it~... chuuuu」</t>
+          <t>「Yaaaah！ Chuchubbu！ Give me more... don’t stop,
+leeeet me have it~... chuuuu」</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -7710,8 +7717,8 @@
       </c>
       <c r="B473" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan intensifies her tongue work, piling on top of
-the pleasure that’s already pushed me to the edge.</t>
+          <t>Rin-chan intensifies her tongue work, piling on top
+of the pleasure that’s already pushed me to the edge.</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -8510,8 +8517,8 @@
       </c>
       <c r="B525" s="1" t="inlineStr">
         <is>
-          <t>I think Rin-chan's running wild right now, but my body
-was burning up and I couldn't stand it either.</t>
+          <t>I think Rin-chan's running wild right now, but my
+body was burning up and I couldn't stand it either.</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -8892,7 +8899,8 @@
       </c>
       <c r="B550" s="1" t="inlineStr">
         <is>
-          <t>「Uah！ U~uaaah！ Don't do it so much... stahp！ Nooo...！」</t>
+          <t>「Uah！ U~uaaah！ Don't do it so much... stahp！
+Nooo...！」</t>
         </is>
       </c>
       <c r="C550" t="n">
@@ -9458,8 +9466,8 @@
       <c r="B587" s="1" t="inlineStr">
         <is>
           <t>The corners of their eyes had started to droop, and
-their whole expression had gone vague… it seemed as if
-they had suddenly begun to feel it all at once.</t>
+their whole expression had gone vague… it seemed as
+if they had suddenly begun to feel it all at once.</t>
         </is>
       </c>
       <c r="C587" t="n">
@@ -9829,8 +9837,8 @@
       </c>
       <c r="B611" s="1" t="inlineStr">
         <is>
-          <t>Ri-Rin-chan is rubbing my penis against her crotch and
-she's feeling it...</t>
+          <t>Ri-Rin-chan is rubbing my penis against her crotch
+and she's feeling it...</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -10028,8 +10036,8 @@
       </c>
       <c r="B624" s="1" t="inlineStr">
         <is>
-          <t>The moment it does, my body jumps and starts trembling
-uncontrollably.</t>
+          <t>The moment it does, my body jumps and starts
+trembling uncontrollably.</t>
         </is>
       </c>
       <c r="C624" t="n">
@@ -10584,9 +10592,9 @@
       </c>
       <c r="B660" s="1" t="inlineStr">
         <is>
-          <t>Even though I've been the one getting blamed the whole
-time, thinking about what's coming makes me feel mean
-and teasing.</t>
+          <t>Even though I've been the one getting blamed the
+whole time, thinking about what's coming makes me
+feel mean and teasing.</t>
         </is>
       </c>
       <c r="C660" t="n">
@@ -10771,7 +10779,8 @@
       </c>
       <c r="B672" s="1" t="inlineStr">
         <is>
-          <t>「Mm, uh… I'll plug that pee-wet pussy with my penis…！」</t>
+          <t>「Mm, uh… I'll plug that pee-wet pussy with my
+penis…！」</t>
         </is>
       </c>
       <c r="C672" t="n">
@@ -10817,8 +10826,8 @@
       </c>
       <c r="B675" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan, who had completely believed my words, lifted
-her hips up toward me.</t>
+          <t>Rin-chan, who had completely believed my words,
+lifted her hips up toward me.</t>
         </is>
       </c>
       <c r="C675" t="n">
@@ -11172,8 +11181,8 @@
       </c>
       <c r="B698" s="1" t="inlineStr">
         <is>
-          <t>Even so, her body immediately tries to get used to it,
-making her juices gush and spill out.</t>
+          <t>Even so, her body immediately tries to get used to
+it, making her juices gush and spill out.</t>
         </is>
       </c>
       <c r="C698" t="n">
@@ -11263,8 +11272,8 @@
       </c>
       <c r="B704" s="1" t="inlineStr">
         <is>
-          <t>The penis is being squeezed tight from the base to the
-tip, it's almost painful.</t>
+          <t>The penis is being squeezed tight from the base to
+the tip, it's almost painful.</t>
         </is>
       </c>
       <c r="C704" t="n">
@@ -11461,8 +11470,9 @@
       </c>
       <c r="B717" s="1" t="inlineStr">
         <is>
-          <t>...She's drunk, so her words and actions get all mixed
-up, but she still seems to want to make me feel good.</t>
+          <t>...She's drunk, so her words and actions get all
+mixed up, but she still seems to want to make me feel
+good.</t>
         </is>
       </c>
       <c r="C717" t="n">
@@ -11660,7 +11670,8 @@
       </c>
       <c r="B730" s="1" t="inlineStr">
         <is>
-          <t>「...So then, I'll be the one to make a move, okay...？」</t>
+          <t>「...So then, I'll be the one to make a move,
+okay...？」</t>
         </is>
       </c>
       <c r="C730" t="n">
@@ -11705,8 +11716,8 @@
       </c>
       <c r="B733" s="1" t="inlineStr">
         <is>
-          <t>When I try rocking my hips upward, Rin-chan lets out a
-squeezed, high-pitched cry.</t>
+          <t>When I try rocking my hips upward, Rin-chan lets out
+a squeezed, high-pitched cry.</t>
         </is>
       </c>
       <c r="C733" t="n">
@@ -11905,8 +11916,8 @@
       <c r="B746" s="1" t="inlineStr">
         <is>
           <t>Rin-chan seemed to like this hip movement, and she
-started grinding insistently, back and forth, back and
-forth.</t>
+started grinding insistently, back and forth, back
+and forth.</t>
         </is>
       </c>
       <c r="C746" t="n">
@@ -12194,8 +12205,8 @@
       </c>
       <c r="B765" s="1" t="inlineStr">
         <is>
-          <t>「Nnnu, hah... aha！ Me too... hah, hah！ It feels！ Good！
-Amazing！」</t>
+          <t>「Nnnu, hah... aha！ Me too... hah, hah！ It feels！
+Good！ Amazing！」</t>
         </is>
       </c>
       <c r="C765" t="n">
@@ -12273,8 +12284,8 @@
       </c>
       <c r="B770" s="1" t="inlineStr">
         <is>
-          <t>「Funyaa... my stomach, my stomach... guu, gu！ Fuhaa...
-it's rubbing...！」</t>
+          <t>「Funyaa... my stomach, my stomach... guu, gu！
+Fuhaa... it's rubbing...！」</t>
         </is>
       </c>
       <c r="C770" t="n">
@@ -12597,8 +12608,8 @@
       </c>
       <c r="B791" s="1" t="inlineStr">
         <is>
-          <t>I shot back while lifting my hips, and Rin-chan smiled
-faintly.</t>
+          <t>I shot back while lifting my hips, and Rin-chan
+smiled faintly.</t>
         </is>
       </c>
       <c r="C791" t="n">
@@ -12613,8 +12624,8 @@
       </c>
       <c r="B792" s="1" t="inlineStr">
         <is>
-          <t>That expression — her tongue hanging out and breathing
-harshly — is unbearably arousing...！</t>
+          <t>That expression — her tongue hanging out and
+breathing harshly — is unbearably arousing...！</t>
         </is>
       </c>
       <c r="C792" t="n">
@@ -12722,8 +12733,8 @@
       </c>
       <c r="B799" s="1" t="inlineStr">
         <is>
-          <t>「Nn… n~u！  brr brr srrr no~… fwah！  don't stop, nyaah…
-unyaah！」</t>
+          <t>「Nn… n~u！  brr brr srrr no~… fwah！  don't stop,
+nyaah… unyaah！」</t>
         </is>
       </c>
       <c r="C799" t="n">
@@ -13184,8 +13195,8 @@
       </c>
       <c r="B829" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan’s begging was the final blow, pushing me past
-my limit！</t>
+          <t>Rin-chan’s begging was the final blow, pushing me
+past my limit！</t>
         </is>
       </c>
       <c r="C829" t="n">
@@ -13828,9 +13839,9 @@
       </c>
       <c r="B871" s="1" t="inlineStr">
         <is>
-          <t>I, too, got drawn in and when I looked at the junction
-I could see a cloudy fluid, like vaginal juices
-diluted with semen, leaking out.</t>
+          <t>I, too, got drawn in and when I looked at the
+junction I could see a cloudy fluid, like vaginal
+juices diluted with semen, leaking out.</t>
         </is>
       </c>
       <c r="C871" t="n">
@@ -13845,8 +13856,8 @@
       </c>
       <c r="B872" s="1" t="inlineStr">
         <is>
-          <t>The penis that came out no longer sealed anything, and
-its juices ran from my hips down to my feet.</t>
+          <t>The penis that came out no longer sealed anything,
+and its juices ran from my hips down to my feet.</t>
         </is>
       </c>
       <c r="C872" t="n">
@@ -13939,9 +13950,9 @@
       </c>
       <c r="B878" s="1" t="inlineStr">
         <is>
-          <t>I must have liked the taste of the semen so much that,
-as if it had become a habit, I brought it to my mouth
-again and again.</t>
+          <t>I must have liked the taste of the semen so much
+that, as if it had become a habit, I brought it to my
+mouth again and again.</t>
         </is>
       </c>
       <c r="C878" t="n">
@@ -14048,8 +14059,8 @@
       </c>
       <c r="B885" s="1" t="inlineStr">
         <is>
-          <t>If she keeps pressuring me like this, I might actually
-end up having to lick my own semen….</t>
+          <t>If she keeps pressuring me like this, I might
+actually end up having to lick my own semen….</t>
         </is>
       </c>
       <c r="C885" t="n">
@@ -14079,8 +14090,8 @@
       </c>
       <c r="B887" s="1" t="inlineStr">
         <is>
-          <t>「Heh heh, huh！ I think I might come to like you… maybe
-next in line after my wisukii bonbon…」</t>
+          <t>「Heh heh, huh！ I think I might come to like you…
+maybe next in line after my wisukii bonbon…」</t>
         </is>
       </c>
       <c r="C887" t="n">
@@ -14491,8 +14502,8 @@
       </c>
       <c r="B914" s="1" t="inlineStr">
         <is>
-          <t>But if Rin-chan gets this horny, maybe I wouldn't mind
-letting her eat it again...</t>
+          <t>But if Rin-chan gets this horny, maybe I wouldn't
+mind letting her eat it again...</t>
         </is>
       </c>
       <c r="C914" t="n">

--- a/processed_ruby_restored_xlsx/sc231_凛３：酔っ払ってＨ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc231_凛３：酔っ払ってＨ.ss.xlsx
@@ -839,7 +839,7 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>Whether she truly understands... I won't ask.</t>
+          <t>Whether they truly understand... I won't ask.</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>「Niini is amazing. I can make Napolitan, and I can
+          <t>「Niini is amazing. He can make Napolitan, and he can
 even do an American...」</t>
         </is>
       </c>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>「Ah— geez, Niini is hopeless~... mixing up what my
+          <t>「Ah— geez, Niini is hopeless~... mixing up what his
 lover says with what someone else says~」</t>
         </is>
       </c>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>「…But only two today, okay？」</t>
+          <t>…But only two today, okay？</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... cheapskate, I think five is fine.」</t>
+          <t>Mmm... cheapskate, I think five is fine.</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>Oh no, is she already drunk...！？</t>
+          <t>Oh no, is she already drunk...！？"</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -4061,9 +4061,9 @@
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t>Besides, I've only seen a single stylized panel, so
-when I actually try to take it in it doesn't work
-like in the comic, and I look totally flustered.</t>
+          <t>Besides, he's only seen a single stylized panel, so
+when he actually tries to take it in it doesn't work
+like in the comic, and he looks totally flustered.</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4768,9 +4768,9 @@
       <c r="B282" s="1" t="inlineStr">
         <is>
           <t>In the manga, the guy's reactions to getting kissed
-on my penis are shown in speech bubbles, so I figured
-my reaction would be pretty much the same as in the
-comic.</t>
+on his penis are shown in speech bubbles, so I
+figured my reaction would be pretty much the same as
+in the comic.</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t>「Uwaaah！ So sudden... uwa, hah！」</t>
+          <t>Uwaaah！ So sudden... uwa, hah！</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="B380" s="1" t="inlineStr">
         <is>
-          <t>「Uah！ Ugh, it hurts！」</t>
+          <t>Uah！ Ugh, it hurts！</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="B383" s="1" t="inlineStr">
         <is>
-          <t>「Hah, hah！ R-Rin... did I do something？」</t>
+          <t>Hah, hah！ R-Rin... did I do something？</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t>「Ah... please don't bite...？」</t>
+          <t>Ah... please don't bite...？</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B410" s="1" t="inlineStr">
         <is>
-          <t>She tightly puckers her mouth and keeps giving my
+          <t>She tightly puckers her mouth and keeps giving his
 penis intense stimulation……。</t>
         </is>
       </c>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="B413" s="1" t="inlineStr">
         <is>
-          <t>……This time her tongue starts to wrap around mine
+          <t>……This time her tongue starts to wrap around his
 penis……！</t>
         </is>
       </c>
@@ -6831,8 +6831,8 @@
       </c>
       <c r="B416" s="1" t="inlineStr">
         <is>
-          <t>「Ah, uaaah...！ If you do it like that... ugh, ha！ I'm
-going to come... uuu...！」</t>
+          <t>Ah, uaaah...！ If you do it like that... ugh, ha！ I'm
+going to come... uuu...！</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="B477" s="1" t="inlineStr">
         <is>
-          <t>Byurubyu byuu！ Doppyu, dogutokuu！</t>
+          <t>Byurubyu byuu！ Doppyu, dogutokuu！"</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="B484" s="1" t="inlineStr">
         <is>
-          <t>Byuppyruu！　Byuhyupyu！</t>
+          <t>Byuppyruu！　Byuhyupyu！"</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="B488" s="1" t="inlineStr">
         <is>
-          <t>「Nhm!  Nn!  Kuuh…  Gokuu…  Gokkuu…」</t>
+          <t>Nhm!  Nn!  Kuuh…  Gokuu…  Gokkuu…</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -7962,7 +7962,7 @@
       <c r="B489" s="1" t="inlineStr">
         <is>
           <t>Rin-chan, who had been ejaculated into her mouth,
-grimaced, yet pressed her lips to me and sucked.</t>
+grimaced, yet pressed her lips to him and sucked.</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -8145,8 +8145,8 @@
       </c>
       <c r="B501" s="1" t="inlineStr">
         <is>
-          <t>「Ufuu...！ There's still some left... Smooch！
-Jup-puuu...」</t>
+          <t>Ufuu...！ There's still some left... Smooch！
+Jup-puuu...</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="B503" s="1" t="inlineStr">
         <is>
-          <t>「Aaaahhh！ I just finished cumming, and yet...！」</t>
+          <t>Aaaahhh！ I just finished cumming, and yet...！</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="B527" s="1" t="inlineStr">
         <is>
-          <t>「Konrohaa... umm, you know？ Fufu, fuh！」</t>
+          <t>Konrohaa... umm, you know？ Fufu, fuh！</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="B548" s="1" t="inlineStr">
         <is>
-          <t>「Fuuuun...？ Naughty Niini... here I come！ Ei, ei！」</t>
+          <t>Fuuuun...？ Naughty Niini... here I come！ Ei, ei！</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -9082,7 +9082,7 @@
       <c r="B562" s="1" t="inlineStr">
         <is>
           <t>Facing Rin-chan who plays without holding back,
-there's no way I could say no.</t>
+there's no way he could say no.</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -9191,7 +9191,7 @@
         <is>
           <t>Her speech is slurred and the act itself is getting
 strange, but the way she presses her between-her-legs
-against me is maddening.</t>
+against him is maddening.</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -9497,8 +9497,8 @@
       </c>
       <c r="B589" s="1" t="inlineStr">
         <is>
-          <t>「Haa... nn！ Fuaa... Rin's between my legs is all wet
-and gooey...」</t>
+          <t>Haa... nn！ Fuaa... Rin's between my legs is all wet
+and gooey...</t>
         </is>
       </c>
       <c r="C589" t="n">
@@ -9528,8 +9528,8 @@
       </c>
       <c r="B591" s="1" t="inlineStr">
         <is>
-          <t>「Uh... yeah, because it's right, I can tell really
-well...？」</t>
+          <t>Uh... yeah, because it's right, I can tell really
+well...？</t>
         </is>
       </c>
       <c r="C591" t="n">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="B678" s="1" t="inlineStr">
         <is>
-          <t>「Well then... I'll... wash it, okay...？」</t>
+          <t>Well then... I'll... wash it, okay...？</t>
         </is>
       </c>
       <c r="C678" t="n">
@@ -11242,7 +11242,7 @@
       </c>
       <c r="B702" s="1" t="inlineStr">
         <is>
-          <t>「O-ooh…！」</t>
+          <t>O-ooh…！</t>
         </is>
       </c>
       <c r="C702" t="n">
@@ -11578,7 +11578,7 @@
       </c>
       <c r="B724" s="1" t="inlineStr">
         <is>
-          <t>「Nnfu, fuu... fufuu, hah！ Haa, haa...」</t>
+          <t>Nnfu, fuu... fufuu, hah！ Haa, haa...</t>
         </is>
       </c>
       <c r="C724" t="n">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="B737" s="1" t="inlineStr">
         <is>
-          <t>Even though I'm drunk and not thinking straight, my
+          <t>Even though he's drunk and not thinking straight, his
 learning ability in this kind of thing is amazing…….</t>
         </is>
       </c>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="B739" s="1" t="inlineStr">
         <is>
-          <t>「Aaah！ That feels so good……！」</t>
+          <t>Aaah！ That feels so good……！</t>
         </is>
       </c>
       <c r="C739" t="n">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="B741" s="1" t="inlineStr">
         <is>
-          <t>「Fuhih, fuu！ Niini's... mmm, yeah……！」</t>
+          <t>Fuhih, fuu！ Niini's... mmm, yeah……！</t>
         </is>
       </c>
       <c r="C741" t="n">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="B743" s="1" t="inlineStr">
         <is>
-          <t>「Aguu… uuu！ Ri, Rin-chan… haa…！」</t>
+          <t>Aguu… uuu！ Ri, Rin-chan… haa…！</t>
         </is>
       </c>
       <c r="C743" t="n">
@@ -11899,8 +11899,7 @@
       </c>
       <c r="B745" s="1" t="inlineStr">
         <is>
-          <t>「Fah！ This is amaaazing… it feels so good, keep
-going…」</t>
+          <t>Fah！ This is amaaazing… it feels so good, keep going…</t>
         </is>
       </c>
       <c r="C745" t="n">
@@ -11947,7 +11946,7 @@
       </c>
       <c r="B748" s="1" t="inlineStr">
         <is>
-          <t>「Nfu！ Niini… ehehe！ Rin… can do it… nngh？」</t>
+          <t>Nfu！ Niini… ehehe！ Rin… can do it… nngh？</t>
         </is>
       </c>
       <c r="C748" t="n">
@@ -12346,7 +12345,7 @@
       </c>
       <c r="B774" s="1" t="inlineStr">
         <is>
-          <t>This... is unbearable...！</t>
+          <t>This... is unbearable...！"</t>
         </is>
       </c>
       <c r="C774" t="n">
@@ -12531,8 +12530,8 @@
       </c>
       <c r="B786" s="1" t="inlineStr">
         <is>
-          <t>「Nn~ fufuu！  Niini... your face is getting all
-nasty/turned-on-looking... nfufufuu...！」</t>
+          <t>Nn~ fufuu！  Niini... your face is getting all
+nasty/turned-on-looking... nfufufuu...！</t>
         </is>
       </c>
       <c r="C786" t="n">
@@ -12655,8 +12654,8 @@
       </c>
       <c r="B794" s="1" t="inlineStr">
         <is>
-          <t>「Haah... ah！ Nnah！ Rin's body... is getting so
-naughty！ It's getting way too much！」</t>
+          <t>Haah... ah！ Nnah！ Rin's body... is getting so
+naughty！ It's getting way too much！</t>
         </is>
       </c>
       <c r="C794" t="n">
@@ -12733,8 +12732,8 @@
       </c>
       <c r="B799" s="1" t="inlineStr">
         <is>
-          <t>「Nn… n~u！  brr brr srrr no~… fwah！  don't stop,
-nyaah… unyaah！」</t>
+          <t>Nn… n~u！  brr brr srrr no~… fwah！  don't stop, nyaah…
+unyaah！</t>
         </is>
       </c>
       <c r="C799" t="n">
@@ -12980,7 +12979,7 @@
       <c r="B815" s="1" t="inlineStr">
         <is>
           <t>The orgasm was finally swelling up, the intense
-pleasure making even discomfort flicker through me.</t>
+pleasure making even discomfort flicker through him.</t>
         </is>
       </c>
       <c r="C815" t="n">
@@ -12995,8 +12994,9 @@
       </c>
       <c r="B816" s="1" t="inlineStr">
         <is>
-          <t>But I lost control of my hips to the point I didn't
-even know how I was moving, thrusting violently.</t>
+          <t>But he lost control of his hips to the point he
+didn't even know how he was moving, thrusting
+violently.</t>
         </is>
       </c>
       <c r="C816" t="n">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="B819" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan was thoroughly pleased by my fierce hip
+          <t>Rin-chan was thoroughly pleased by his fierce hip
 action.</t>
         </is>
       </c>
@@ -13195,8 +13195,8 @@
       </c>
       <c r="B829" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan’s begging was the final blow, pushing me
-past my limit！</t>
+          <t>Rin-chan’s begging was the final blow, pushing him
+past his limit！</t>
         </is>
       </c>
       <c r="C829" t="n">
@@ -13380,8 +13380,8 @@
       </c>
       <c r="B841" s="1" t="inlineStr">
         <is>
-          <t>Stimulated by that voice, my penis keeps ejaculating,
-continuing to spew out semen.</t>
+          <t>Stimulated by that voice, his penis keeps
+ejaculating, continuing to spew out semen.</t>
         </is>
       </c>
       <c r="C841" t="n">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="B847" s="1" t="inlineStr">
         <is>
-          <t>「Aahhh… it feels so good！ It's too good…」</t>
+          <t>Aahhh… it feels so good！ It's too good…</t>
         </is>
       </c>
       <c r="C847" t="n">
@@ -13503,7 +13503,7 @@
       <c r="B849" s="1" t="inlineStr">
         <is>
           <t>Her pussy pulsed again and again, as if still wanting
-more, squeezing out my semen….</t>
+more, squeezing out his semen….</t>
         </is>
       </c>
       <c r="C849" t="n">
@@ -13950,9 +13950,9 @@
       </c>
       <c r="B878" s="1" t="inlineStr">
         <is>
-          <t>I must have liked the taste of the semen so much
-that, as if it had become a habit, I brought it to my
-mouth again and again.</t>
+          <t>He must have liked the taste of the semen so much
+that, as if it had become a habit, he brought it to
+his mouth again and again.</t>
         </is>
       </c>
       <c r="C878" t="n">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="B883" s="1" t="inlineStr">
         <is>
-          <t>「N-no, w-wait！ I'll pass…！」</t>
+          <t>N-no, w-wait！ I」ll pass…！</t>
         </is>
       </c>
       <c r="C883" t="n">
@@ -14564,8 +14564,8 @@
       </c>
       <c r="B918" s="1" t="inlineStr">
         <is>
-          <t>「Chupuu... fuu！ So— for now... I'll put up with
-Niini's naughty juice... chupuu！」</t>
+          <t>Chupuu... fuu！ So— for now... I'll put up with
+Niini's naughty juice... chupuu！</t>
         </is>
       </c>
       <c r="C918" t="n">
